--- a/diseases/d045/2026-2029.xlsx
+++ b/diseases/d045/2026-2029.xlsx
@@ -45071,12 +45071,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -45101,7 +45101,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -45110,81 +45110,100 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O247" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R247" t="n">
-        <v>0.002450425222697299</v>
+        <v>0</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ247" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR247" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS247" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
       <c r="AT247" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -45211,17 +45230,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -45246,7 +45265,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -45260,76 +45279,170 @@
       <c r="O248" t="n">
         <v>0</v>
       </c>
-      <c r="R248" t="n">
-        <v>0</v>
-      </c>
-      <c r="S248" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>Echinokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ248" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK248" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM248" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN248" t="b">
+        <v>1</v>
       </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ248" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR248" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS248" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
       <c r="AT248" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -45391,7 +45504,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -45400,13 +45513,13 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O249" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R249" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
@@ -45536,7 +45649,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -45651,12 +45764,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -45681,22 +45794,22 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N251" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O251" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R251" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S251" t="inlineStr">
         <is>
@@ -45729,42 +45842,42 @@
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45796,12 +45909,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -45826,12 +45939,12 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N252" t="n">
@@ -45848,87 +45961,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U252" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="AA252" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ252" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR252" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS252" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr"/>
       <c r="AT252" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45955,17 +46049,17 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -46004,170 +46098,76 @@
       <c r="O253" t="n">
         <v>0</v>
       </c>
-      <c r="U253" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="V253" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="W253" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X253" t="inlineStr">
-        <is>
-          <t>Echinococcus</t>
-        </is>
-      </c>
-      <c r="Y253" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z253" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA253" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB253" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD253" t="inlineStr">
+      <c r="R253" t="n">
+        <v>0</v>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO253" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP253" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR253" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr"/>
+      <c r="AT253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU253" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV253" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE253" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF253" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG253" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH253" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI253" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ253" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK253" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
-        </is>
-      </c>
-      <c r="AM253" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN253" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO253" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP253" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ253" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR253" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS253" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="AT253" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU253" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV253" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -46199,12 +46199,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -46253,7 +46253,7 @@
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -46273,7 +46273,7 @@
       </c>
       <c r="AQ254" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR254" t="inlineStr">
@@ -46283,7 +46283,7 @@
       </c>
       <c r="AS254" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT254" t="n">
@@ -46291,47 +46291,47 @@
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -46363,12 +46363,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -46409,22 +46409,22 @@
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="V255" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="W255" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X255" t="inlineStr">
         <is>
-          <t>Ekinokokkose</t>
+          <t>Echinococcus</t>
         </is>
       </c>
       <c r="Y255" t="inlineStr">
@@ -46449,7 +46449,7 @@
       </c>
       <c r="AC255" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD255" t="inlineStr">
@@ -46484,17 +46484,17 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
         </is>
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -46512,7 +46512,7 @@
       </c>
       <c r="AQ255" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR255" t="inlineStr">
@@ -46522,7 +46522,7 @@
       </c>
       <c r="AS255" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT255" t="n">
@@ -46530,45 +46530,448 @@
       </c>
       <c r="AU255" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV255" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW255" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX255" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA255" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB255" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC255" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N256" t="n">
+        <v>0</v>
+      </c>
+      <c r="O256" t="n">
+        <v>0</v>
+      </c>
+      <c r="R256" t="n">
+        <v>0</v>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO256" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP256" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ256" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT256" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU256" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV255" t="inlineStr">
+      <c r="AV256" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW255" t="inlineStr">
+      <c r="AW256" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX255" t="inlineStr">
+      <c r="AX256" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY255" t="inlineStr">
+      <c r="AY256" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ255" t="inlineStr">
+      <c r="AZ256" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA255" t="inlineStr">
+      <c r="BA256" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB255" t="inlineStr">
+      <c r="BB256" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC255" t="inlineStr">
+      <c r="BC256" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N257" t="n">
+        <v>0</v>
+      </c>
+      <c r="O257" t="n">
+        <v>0</v>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>Ekinokokkose</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD257" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE257" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF257" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG257" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH257" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI257" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ257" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM257" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN257" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO257" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP257" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ257" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR257" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT257" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU257" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV257" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW257" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX257" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY257" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA257" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB257" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC257" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -46690,7 +47093,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10">
@@ -46700,7 +47103,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -46720,7 +47123,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d045/2026-2029.xlsx
+++ b/diseases/d045/2026-2029.xlsx
@@ -44304,13 +44304,13 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R243" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
@@ -44468,10 +44468,10 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U244" t="inlineStr">
         <is>
@@ -46054,12 +46054,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -46084,22 +46084,22 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R253" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S253" t="inlineStr">
         <is>
@@ -46132,42 +46132,42 @@
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46199,12 +46199,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -46251,87 +46251,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U254" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="AA254" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ254" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR254" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS254" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr"/>
       <c r="AT254" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -46358,7 +46339,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -46407,98 +46388,23 @@
       <c r="O255" t="n">
         <v>0</v>
       </c>
+      <c r="R255" t="n">
+        <v>0</v>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U255" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
-      <c r="V255" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="W255" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X255" t="inlineStr">
-        <is>
-          <t>Echinococcus</t>
-        </is>
-      </c>
-      <c r="Y255" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z255" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA255" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD255" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE255" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF255" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG255" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH255" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI255" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ255" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK255" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
-        </is>
-      </c>
-      <c r="AM255" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN255" t="b">
-        <v>1</v>
       </c>
       <c r="AO255" t="inlineStr">
         <is>
@@ -46597,17 +46503,17 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -46646,17 +46552,34 @@
       <c r="O256" t="n">
         <v>0</v>
       </c>
-      <c r="R256" t="n">
-        <v>0</v>
-      </c>
-      <c r="S256" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U256" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>Echinococcus</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
@@ -46664,6 +46587,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD256" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF256" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG256" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH256" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI256" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ256" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK256" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
+        </is>
+      </c>
+      <c r="AM256" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN256" t="b">
+        <v>1</v>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -46676,7 +46657,7 @@
       </c>
       <c r="AQ256" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR256" t="inlineStr">
@@ -46686,7 +46667,7 @@
       </c>
       <c r="AS256" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT256" t="n">
@@ -46694,47 +46675,47 @@
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -46761,7 +46742,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -46810,98 +46791,23 @@
       <c r="O257" t="n">
         <v>0</v>
       </c>
+      <c r="R257" t="n">
+        <v>0</v>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U257" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
-      <c r="V257" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W257" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X257" t="inlineStr">
-        <is>
-          <t>Ekinokokkose</t>
-        </is>
-      </c>
-      <c r="Y257" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z257" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA257" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB257" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC257" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD257" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE257" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF257" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG257" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH257" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI257" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ257" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK257" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM257" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN257" t="b">
-        <v>1</v>
       </c>
       <c r="AO257" t="inlineStr">
         <is>
@@ -46972,6 +46878,245 @@
         </is>
       </c>
       <c r="BC257" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N258" t="n">
+        <v>0</v>
+      </c>
+      <c r="O258" t="n">
+        <v>0</v>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>Ekinokokkose</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD258" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE258" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF258" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG258" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH258" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI258" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ258" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK258" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM258" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN258" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO258" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP258" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ258" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT258" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU258" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV258" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA258" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB258" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC258" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -47093,7 +47238,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10">
@@ -47103,7 +47248,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -47155,7 +47300,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4822</v>
+        <v>4824</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d045/2026-2029.xlsx
+++ b/diseases/d045/2026-2029.xlsx
@@ -44707,13 +44707,13 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R245" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -44871,10 +44871,10 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U246" t="inlineStr">
         <is>
@@ -47300,7 +47300,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4824</v>
+        <v>4825</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d045/2026-2029.xlsx
+++ b/diseases/d045/2026-2029.xlsx
@@ -44265,12 +44265,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -44304,100 +44304,84 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>1</v>
+        <v>326</v>
       </c>
       <c r="O243" t="n">
-        <v>1</v>
+        <v>326</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>0</v>
       </c>
       <c r="R243" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.02307288197162032</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="AA243" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO243" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ243" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR243" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS243" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr"/>
       <c r="AT243" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -44424,7 +44408,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -44473,98 +44457,23 @@
       <c r="O244" t="n">
         <v>1</v>
       </c>
+      <c r="R244" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U244" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
-      <c r="V244" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="W244" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X244" t="inlineStr">
-        <is>
-          <t>Echinococcus</t>
-        </is>
-      </c>
-      <c r="Y244" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z244" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA244" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB244" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC244" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD244" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE244" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF244" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG244" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH244" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI244" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ244" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK244" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
-        </is>
-      </c>
-      <c r="AM244" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN244" t="b">
-        <v>1</v>
       </c>
       <c r="AO244" t="inlineStr">
         <is>
@@ -44663,17 +44572,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -44707,22 +44616,39 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O245" t="n">
-        <v>2</v>
-      </c>
-      <c r="R245" t="n">
-        <v>0.03537951651591013</v>
-      </c>
-      <c r="S245" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>Echinococcus</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -44730,6 +44656,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF245" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH245" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI245" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ245" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK245" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
+        </is>
+      </c>
+      <c r="AM245" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN245" t="b">
+        <v>1</v>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -44742,7 +44726,7 @@
       </c>
       <c r="AQ245" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR245" t="inlineStr">
@@ -44752,7 +44736,7 @@
       </c>
       <c r="AS245" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT245" t="n">
@@ -44760,47 +44744,47 @@
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -44827,7 +44811,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -44876,98 +44860,23 @@
       <c r="O246" t="n">
         <v>2</v>
       </c>
+      <c r="R246" t="n">
+        <v>0.03537951651591013</v>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U246" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
-      <c r="V246" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W246" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X246" t="inlineStr">
-        <is>
-          <t>Ekinokokkose</t>
-        </is>
-      </c>
-      <c r="Y246" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z246" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA246" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB246" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD246" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE246" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF246" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG246" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH246" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI246" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ246" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK246" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM246" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN246" t="b">
-        <v>1</v>
       </c>
       <c r="AO246" t="inlineStr">
         <is>
@@ -45066,17 +44975,17 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -45110,22 +45019,39 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O247" t="n">
-        <v>0</v>
-      </c>
-      <c r="R247" t="n">
-        <v>0</v>
-      </c>
-      <c r="S247" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>Ekinokokkose</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -45133,6 +45059,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD247" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF247" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG247" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH247" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI247" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ247" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK247" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM247" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN247" t="b">
+        <v>1</v>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -45155,7 +45139,7 @@
       </c>
       <c r="AS247" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT247" t="n">
@@ -45168,42 +45152,42 @@
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -45230,7 +45214,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -45279,98 +45263,23 @@
       <c r="O248" t="n">
         <v>0</v>
       </c>
+      <c r="R248" t="n">
+        <v>0</v>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U248" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
         </is>
       </c>
-      <c r="V248" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
-        </is>
-      </c>
-      <c r="W248" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X248" t="inlineStr">
-        <is>
-          <t>Echinokockinfektion</t>
-        </is>
-      </c>
-      <c r="Y248" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z248" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA248" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB248" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC248" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD248" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE248" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF248" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG248" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH248" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI248" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ248" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK248" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM248" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN248" t="b">
-        <v>1</v>
       </c>
       <c r="AO248" t="inlineStr">
         <is>
@@ -45469,17 +45378,17 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -45504,7 +45413,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -45513,81 +45422,175 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O249" t="n">
-        <v>3</v>
-      </c>
-      <c r="R249" t="n">
-        <v>0.002450425222697299</v>
-      </c>
-      <c r="S249" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>Echinokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF249" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG249" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH249" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI249" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ249" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK249" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM249" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN249" t="b">
+        <v>1</v>
       </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ249" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR249" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS249" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
       <c r="AT249" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -45649,7 +45652,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -45658,13 +45661,13 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O250" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R250" t="n">
-        <v>0</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
@@ -45794,7 +45797,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -45803,13 +45806,13 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O251" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R251" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S251" t="inlineStr">
         <is>
@@ -45939,7 +45942,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -45948,13 +45951,13 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R252" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -46084,7 +46087,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -46093,13 +46096,13 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O253" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R253" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S253" t="inlineStr">
         <is>
@@ -46199,12 +46202,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -46229,22 +46232,22 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N254" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O254" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R254" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -46277,42 +46280,42 @@
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46344,12 +46347,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -46396,87 +46399,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U255" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="AA255" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ255" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR255" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS255" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr"/>
       <c r="AT255" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -46503,7 +46487,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -46552,98 +46536,23 @@
       <c r="O256" t="n">
         <v>0</v>
       </c>
+      <c r="R256" t="n">
+        <v>0</v>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U256" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
-      <c r="V256" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="W256" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X256" t="inlineStr">
-        <is>
-          <t>Echinococcus</t>
-        </is>
-      </c>
-      <c r="Y256" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z256" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA256" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB256" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC256" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD256" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE256" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF256" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG256" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH256" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI256" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ256" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK256" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
-        </is>
-      </c>
-      <c r="AM256" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN256" t="b">
-        <v>1</v>
       </c>
       <c r="AO256" t="inlineStr">
         <is>
@@ -46742,17 +46651,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -46791,17 +46700,34 @@
       <c r="O257" t="n">
         <v>0</v>
       </c>
-      <c r="R257" t="n">
-        <v>0</v>
-      </c>
-      <c r="S257" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>Echinococcus</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
@@ -46809,6 +46735,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD257" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE257" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF257" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG257" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH257" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI257" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ257" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
+        </is>
+      </c>
+      <c r="AM257" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN257" t="b">
+        <v>1</v>
+      </c>
       <c r="AO257" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -46821,7 +46805,7 @@
       </c>
       <c r="AQ257" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR257" t="inlineStr">
@@ -46831,7 +46815,7 @@
       </c>
       <c r="AS257" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT257" t="n">
@@ -46839,47 +46823,47 @@
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -46906,7 +46890,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -46955,98 +46939,23 @@
       <c r="O258" t="n">
         <v>0</v>
       </c>
+      <c r="R258" t="n">
+        <v>0</v>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U258" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
-      <c r="V258" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W258" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X258" t="inlineStr">
-        <is>
-          <t>Ekinokokkose</t>
-        </is>
-      </c>
-      <c r="Y258" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z258" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA258" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB258" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC258" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD258" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE258" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF258" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG258" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH258" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI258" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ258" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK258" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM258" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN258" t="b">
-        <v>1</v>
       </c>
       <c r="AO258" t="inlineStr">
         <is>
@@ -47117,6 +47026,245 @@
         </is>
       </c>
       <c r="BC258" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N259" t="n">
+        <v>0</v>
+      </c>
+      <c r="O259" t="n">
+        <v>0</v>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X259" t="inlineStr">
+        <is>
+          <t>Ekinokokkose</t>
+        </is>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB259" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD259" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE259" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF259" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG259" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH259" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI259" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ259" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK259" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM259" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN259" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO259" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP259" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ259" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR259" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT259" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU259" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV259" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW259" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX259" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY259" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA259" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB259" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC259" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -47238,7 +47386,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10">
@@ -47248,7 +47396,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
@@ -47300,7 +47448,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4825</v>
+        <v>5151</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d045/2026-2029.xlsx
+++ b/diseases/d045/2026-2029.xlsx
@@ -37822,12 +37822,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -37861,84 +37861,92 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>952</v>
+        <v>1</v>
       </c>
       <c r="O206" t="n">
-        <v>952</v>
-      </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
-      <c r="R206" t="n">
-        <v>0.06737847741405686</v>
+        <v>1</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ECHINOCOCCUS_MULTILOCULARIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ECHINOCOCCUS_MULTILOCULARIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -37965,17 +37973,17 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>CN-AH</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Anhui, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -38009,14 +38017,39 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O207" t="n">
-        <v>0</v>
-      </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>missing_population</t>
+        <v>1</v>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ECHINOCOCCUS_MULTILOCULARIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ECHINOCOCCUS_MULTILOCULARIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>Echinococcus Multilocularis Infection</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -38024,6 +38057,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary Echinococcus multilocularis infection notifications; confirmed cases only. This species-specific source category is narrower than the ontology's all-echinococcosis D045 concept.</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN207" t="b">
+        <v>1</v>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -38031,7 +38122,7 @@
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ207" t="inlineStr">
@@ -38041,55 +38132,55 @@
       </c>
       <c r="AS207" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_ECHINOCOCCOSIS; SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
+          <t>SER_CA_ON_PHO_IDTO_ECHINOCOCCUS_MULTILOCULARIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.ahlx.gov.cn/Jczwgk/showList/1/125024000/page_1.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -38116,17 +38207,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>CN-AH</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Anhui, China</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -38160,170 +38251,84 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="O208" t="n">
-        <v>0</v>
-      </c>
-      <c r="U208" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
-        </is>
-      </c>
-      <c r="V208" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
-        </is>
-      </c>
-      <c r="W208" t="inlineStr">
-        <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
-        </is>
-      </c>
-      <c r="X208" t="inlineStr">
-        <is>
-          <t>包虫病</t>
-        </is>
-      </c>
-      <c r="Y208" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
-        </is>
-      </c>
-      <c r="AA208" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>country:CN-AH:national</t>
-        </is>
-      </c>
-      <c r="AD208" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE208" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF208" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG208" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH208" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI208" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ208" t="inlineStr">
-        <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
-        </is>
-      </c>
-      <c r="AK208" t="inlineStr">
-        <is>
-          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
-        </is>
-      </c>
-      <c r="AM208" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN208" t="b">
-        <v>1</v>
+        <v>952</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>0</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0.06737847741405686</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
-        </is>
-      </c>
-      <c r="AQ208" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_ECHINOCOCCOSIS; SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr"/>
       <c r="AT208" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.ahlx.gov.cn/Jczwgk/showList/1/125024000/page_1.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -38355,12 +38360,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CN-AH</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Anhui, China</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -38394,10 +38399,10 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
@@ -38469,7 +38474,7 @@
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.ahlx.gov.cn/Jczwgk/showList/1/125024000/page_1.html</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
@@ -38506,12 +38511,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CN-AH</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Anhui, China</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -38545,10 +38550,10 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U210" t="inlineStr">
         <is>
@@ -38592,7 +38597,7 @@
       </c>
       <c r="AC210" t="inlineStr">
         <is>
-          <t>country:CN-CQ:national</t>
+          <t>country:CN-AH:national</t>
         </is>
       </c>
       <c r="AD210" t="inlineStr">
@@ -38703,7 +38708,7 @@
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.ahlx.gov.cn/Jczwgk/showList/1/125024000/page_1.html</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
@@ -38740,12 +38745,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -38779,10 +38784,10 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -38854,7 +38859,7 @@
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
@@ -38891,12 +38896,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -38930,10 +38935,10 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U212" t="inlineStr">
         <is>
@@ -38977,7 +38982,7 @@
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-CQ:national</t>
         </is>
       </c>
       <c r="AD212" t="inlineStr">
@@ -39088,7 +39093,7 @@
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
@@ -39125,12 +39130,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -39239,7 +39244,7 @@
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
@@ -39276,12 +39281,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -39362,7 +39367,7 @@
       </c>
       <c r="AC214" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD214" t="inlineStr">
@@ -39473,7 +39478,7 @@
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
@@ -39510,12 +39515,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -39549,10 +39554,10 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
@@ -39624,7 +39629,7 @@
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
@@ -39661,12 +39666,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -39700,10 +39705,10 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U216" t="inlineStr">
         <is>
@@ -39747,7 +39752,7 @@
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD216" t="inlineStr">
@@ -39858,7 +39863,7 @@
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
@@ -39895,12 +39900,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -40009,7 +40014,7 @@
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
@@ -40046,12 +40051,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -40132,7 +40137,7 @@
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr">
@@ -40243,7 +40248,7 @@
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
@@ -40280,12 +40285,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -40319,10 +40324,10 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>655</v>
+        <v>1</v>
       </c>
       <c r="O219" t="n">
-        <v>655</v>
+        <v>1</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
@@ -40394,7 +40399,7 @@
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
@@ -40431,12 +40436,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -40470,10 +40475,10 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>655</v>
+        <v>1</v>
       </c>
       <c r="O220" t="n">
-        <v>655</v>
+        <v>1</v>
       </c>
       <c r="U220" t="inlineStr">
         <is>
@@ -40517,7 +40522,7 @@
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD220" t="inlineStr">
@@ -40628,7 +40633,7 @@
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
@@ -40665,12 +40670,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -40704,10 +40709,10 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>1</v>
+        <v>655</v>
       </c>
       <c r="O221" t="n">
-        <v>1</v>
+        <v>655</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
@@ -40779,7 +40784,7 @@
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
@@ -40816,12 +40821,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -40855,10 +40860,10 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>1</v>
+        <v>655</v>
       </c>
       <c r="O222" t="n">
-        <v>1</v>
+        <v>655</v>
       </c>
       <c r="U222" t="inlineStr">
         <is>
@@ -40902,7 +40907,7 @@
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD222" t="inlineStr">
@@ -41013,7 +41018,7 @@
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
@@ -41050,12 +41055,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -41089,22 +41094,14 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O223" t="n">
-        <v>0</v>
-      </c>
-      <c r="R223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U223" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -41119,22 +41116,17 @@
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ223" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR223" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_230</t>
+          <t>SER_CN_PROV_DC_ECHINOCOCCOSIS; SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="AT223" t="n">
@@ -41142,47 +41134,47 @@
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -41214,12 +41206,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -41253,29 +41245,29 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_230</t>
+          <t>SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="V224" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_230</t>
+          <t>SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X224" t="inlineStr">
         <is>
-          <t>Echinococcus</t>
+          <t>包虫病</t>
         </is>
       </c>
       <c r="Y224" t="inlineStr">
@@ -41285,7 +41277,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -41300,7 +41292,7 @@
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN-SH:national</t>
         </is>
       </c>
       <c r="AD224" t="inlineStr">
@@ -41335,17 +41327,17 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN224" t="b">
@@ -41358,22 +41350,17 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR224" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_230</t>
+          <t>SER_CN_PROV_DC_ECHINOCOCCOSIS; SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="AT224" t="n">
@@ -41381,47 +41368,47 @@
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -41453,12 +41440,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -41507,7 +41494,7 @@
       </c>
       <c r="U225" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -41527,7 +41514,7 @@
       </c>
       <c r="AQ225" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR225" t="inlineStr">
@@ -41537,7 +41524,7 @@
       </c>
       <c r="AS225" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT225" t="n">
@@ -41545,47 +41532,47 @@
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -41617,12 +41604,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -41663,22 +41650,22 @@
       </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="V226" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X226" t="inlineStr">
         <is>
-          <t>Ekinokokkose</t>
+          <t>Echinococcus</t>
         </is>
       </c>
       <c r="Y226" t="inlineStr">
@@ -41703,7 +41690,7 @@
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD226" t="inlineStr">
@@ -41738,17 +41725,17 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
         </is>
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN226" t="b">
@@ -41766,7 +41753,7 @@
       </c>
       <c r="AQ226" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR226" t="inlineStr">
@@ -41776,7 +41763,7 @@
       </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT226" t="n">
@@ -41784,47 +41771,47 @@
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -41856,12 +41843,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -41895,13 +41882,13 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R227" t="n">
-        <v>0.009344880428283346</v>
+        <v>0</v>
       </c>
       <c r="S227" t="inlineStr">
         <is>
@@ -41910,7 +41897,7 @@
       </c>
       <c r="U227" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -41940,7 +41927,7 @@
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT227" t="n">
@@ -41953,42 +41940,42 @@
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -42020,12 +42007,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -42059,29 +42046,29 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="V228" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="W228" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X228" t="inlineStr">
         <is>
-          <t>Echinokockinfektion</t>
+          <t>Ekinokokkose</t>
         </is>
       </c>
       <c r="Y228" t="inlineStr">
@@ -42106,7 +42093,7 @@
       </c>
       <c r="AC228" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD228" t="inlineStr">
@@ -42141,17 +42128,17 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM228" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN228" t="b">
@@ -42179,7 +42166,7 @@
       </c>
       <c r="AS228" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT228" t="n">
@@ -42192,42 +42179,42 @@
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -42259,12 +42246,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -42289,7 +42276,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -42298,81 +42285,100 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R229" t="n">
-        <v>0</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ229" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR229" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS229" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
       <c r="AT229" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -42399,17 +42405,17 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -42434,7 +42440,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -42443,81 +42449,175 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O230" t="n">
-        <v>0</v>
-      </c>
-      <c r="R230" t="n">
-        <v>0</v>
-      </c>
-      <c r="S230" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>Echinokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD230" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF230" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG230" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ230" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK230" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM230" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN230" t="b">
+        <v>1</v>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ230" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR230" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS230" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
       <c r="AT230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -42579,7 +42679,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -42724,7 +42824,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -42869,7 +42969,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -42878,13 +42978,13 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R233" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S233" t="inlineStr">
         <is>
@@ -42984,12 +43084,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -43014,12 +43114,12 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N234" t="n">
@@ -43062,42 +43162,42 @@
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43129,12 +43229,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -43159,23 +43259,26 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O235" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R235" t="n">
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO235" t="inlineStr">
@@ -43204,42 +43307,42 @@
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43271,12 +43374,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -43315,9 +43418,12 @@
       <c r="O236" t="n">
         <v>0</v>
       </c>
+      <c r="R236" t="n">
+        <v>0</v>
+      </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO236" t="inlineStr">
@@ -43351,12 +43457,12 @@
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
@@ -43371,12 +43477,12 @@
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
@@ -43413,12 +43519,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -43493,7 +43599,7 @@
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
@@ -43513,7 +43619,7 @@
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
@@ -43555,12 +43661,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -43635,7 +43741,7 @@
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
@@ -43655,7 +43761,7 @@
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
@@ -43697,12 +43803,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -43777,7 +43883,7 @@
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
@@ -43797,7 +43903,7 @@
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
@@ -43839,12 +43945,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -43919,7 +44025,7 @@
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
@@ -43939,7 +44045,7 @@
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
@@ -43981,12 +44087,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -44061,7 +44167,7 @@
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
@@ -44081,7 +44187,7 @@
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
@@ -44123,12 +44229,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -44203,7 +44309,7 @@
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
@@ -44223,7 +44329,7 @@
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
@@ -44265,12 +44371,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -44304,20 +44410,14 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>326</v>
+        <v>0</v>
       </c>
       <c r="O243" t="n">
-        <v>326</v>
-      </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
-      <c r="R243" t="n">
-        <v>0.02307288197162032</v>
+        <v>0</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO243" t="inlineStr">
@@ -44346,42 +44446,42 @@
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -44413,12 +44513,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -44452,100 +44552,78 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O244" t="n">
-        <v>1</v>
-      </c>
-      <c r="R244" t="n">
-        <v>0.01778809170864137</v>
+        <v>0</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U244" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="AA244" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO244" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ244" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR244" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS244" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr"/>
       <c r="AT244" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -44572,17 +44650,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -44616,175 +44694,84 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>1</v>
+        <v>326</v>
       </c>
       <c r="O245" t="n">
-        <v>1</v>
-      </c>
-      <c r="U245" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="V245" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="W245" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X245" t="inlineStr">
-        <is>
-          <t>Echinococcus</t>
-        </is>
-      </c>
-      <c r="Y245" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z245" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA245" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB245" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC245" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD245" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE245" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF245" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG245" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH245" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI245" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ245" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK245" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
-        </is>
-      </c>
-      <c r="AM245" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN245" t="b">
-        <v>1</v>
+        <v>326</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>0</v>
+      </c>
+      <c r="R245" t="n">
+        <v>0.02307288197162032</v>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO245" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ245" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR245" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS245" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr"/>
       <c r="AT245" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -44816,12 +44803,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -44855,13 +44842,13 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O246" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R246" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -44870,7 +44857,7 @@
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -44890,7 +44877,7 @@
       </c>
       <c r="AQ246" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR246" t="inlineStr">
@@ -44900,7 +44887,7 @@
       </c>
       <c r="AS246" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT246" t="n">
@@ -44908,47 +44895,47 @@
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -44980,12 +44967,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -45019,29 +45006,29 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O247" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="V247" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="W247" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X247" t="inlineStr">
         <is>
-          <t>Ekinokokkose</t>
+          <t>Echinococcus</t>
         </is>
       </c>
       <c r="Y247" t="inlineStr">
@@ -45066,7 +45053,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD247" t="inlineStr">
@@ -45101,17 +45088,17 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
         </is>
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -45129,7 +45116,7 @@
       </c>
       <c r="AQ247" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR247" t="inlineStr">
@@ -45139,7 +45126,7 @@
       </c>
       <c r="AS247" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT247" t="n">
@@ -45147,47 +45134,47 @@
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -45219,12 +45206,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -45258,13 +45245,13 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O248" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R248" t="n">
-        <v>0</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
@@ -45273,7 +45260,7 @@
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -45303,7 +45290,7 @@
       </c>
       <c r="AS248" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT248" t="n">
@@ -45316,42 +45303,42 @@
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -45383,12 +45370,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -45422,29 +45409,29 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O249" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="V249" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="W249" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X249" t="inlineStr">
         <is>
-          <t>Echinokockinfektion</t>
+          <t>Ekinokokkose</t>
         </is>
       </c>
       <c r="Y249" t="inlineStr">
@@ -45469,7 +45456,7 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD249" t="inlineStr">
@@ -45504,17 +45491,17 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -45542,7 +45529,7 @@
       </c>
       <c r="AS249" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT249" t="n">
@@ -45555,42 +45542,42 @@
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -45622,12 +45609,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -45652,7 +45639,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -45661,81 +45648,100 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O250" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R250" t="n">
-        <v>0.002450425222697299</v>
+        <v>0</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ250" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR250" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS250" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
       <c r="AT250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -45762,17 +45768,17 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -45797,7 +45803,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -45811,76 +45817,170 @@
       <c r="O251" t="n">
         <v>0</v>
       </c>
-      <c r="R251" t="n">
-        <v>0</v>
-      </c>
-      <c r="S251" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>Echinokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF251" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH251" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI251" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ251" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK251" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM251" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN251" t="b">
+        <v>1</v>
       </c>
       <c r="AO251" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ251" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR251" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS251" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
       <c r="AT251" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -45942,7 +46042,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -45951,13 +46051,13 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O252" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R252" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -46087,7 +46187,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -46232,7 +46332,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -46347,12 +46447,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -46377,12 +46477,12 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N255" t="n">
@@ -46425,42 +46525,42 @@
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46492,12 +46592,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -46522,109 +46622,90 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R256" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U256" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="AA256" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO256" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ256" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR256" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr"/>
       <c r="AT256" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46651,17 +46732,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -46700,170 +46781,76 @@
       <c r="O257" t="n">
         <v>0</v>
       </c>
-      <c r="U257" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="V257" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="W257" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X257" t="inlineStr">
-        <is>
-          <t>Echinococcus</t>
-        </is>
-      </c>
-      <c r="Y257" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z257" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA257" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB257" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC257" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD257" t="inlineStr">
+      <c r="R257" t="n">
+        <v>0</v>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO257" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP257" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR257" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr"/>
+      <c r="AT257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU257" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV257" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE257" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF257" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG257" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH257" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI257" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ257" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK257" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
-        </is>
-      </c>
-      <c r="AM257" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN257" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO257" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP257" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ257" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR257" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS257" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="AT257" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU257" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV257" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -46895,12 +46882,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -46949,7 +46936,7 @@
       </c>
       <c r="U258" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
@@ -46969,7 +46956,7 @@
       </c>
       <c r="AQ258" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR258" t="inlineStr">
@@ -46979,7 +46966,7 @@
       </c>
       <c r="AS258" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT258" t="n">
@@ -46987,47 +46974,47 @@
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -47059,12 +47046,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -47105,22 +47092,22 @@
       </c>
       <c r="U259" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="V259" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="W259" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X259" t="inlineStr">
         <is>
-          <t>Ekinokokkose</t>
+          <t>Echinococcus</t>
         </is>
       </c>
       <c r="Y259" t="inlineStr">
@@ -47145,7 +47132,7 @@
       </c>
       <c r="AC259" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD259" t="inlineStr">
@@ -47180,17 +47167,17 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
         </is>
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN259" t="b">
@@ -47208,7 +47195,7 @@
       </c>
       <c r="AQ259" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR259" t="inlineStr">
@@ -47218,7 +47205,7 @@
       </c>
       <c r="AS259" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT259" t="n">
@@ -47226,45 +47213,448 @@
       </c>
       <c r="AU259" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV259" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW259" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX259" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY259" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA259" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB259" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC259" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N260" t="n">
+        <v>0</v>
+      </c>
+      <c r="O260" t="n">
+        <v>0</v>
+      </c>
+      <c r="R260" t="n">
+        <v>0</v>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO260" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP260" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ260" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR260" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT260" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU260" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV259" t="inlineStr">
+      <c r="AV260" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW259" t="inlineStr">
+      <c r="AW260" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX259" t="inlineStr">
+      <c r="AX260" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY259" t="inlineStr">
+      <c r="AY260" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ259" t="inlineStr">
+      <c r="AZ260" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA259" t="inlineStr">
+      <c r="BA260" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB259" t="inlineStr">
+      <c r="BB260" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC259" t="inlineStr">
+      <c r="BC260" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N261" t="n">
+        <v>0</v>
+      </c>
+      <c r="O261" t="n">
+        <v>0</v>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>Ekinokokkose</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD261" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE261" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF261" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG261" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH261" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI261" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ261" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK261" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM261" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN261" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO261" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP261" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ261" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR261" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT261" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU261" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV261" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW261" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX261" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY261" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA261" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB261" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC261" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -47386,7 +47776,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10">
@@ -47396,7 +47786,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11">
@@ -47416,7 +47806,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -47448,7 +47838,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5151</v>
+        <v>5152</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d045/2026-2029.xlsx
+++ b/diseases/d045/2026-2029.xlsx
@@ -47660,6 +47660,151 @@
         </is>
       </c>
     </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N262" t="n">
+        <v>0</v>
+      </c>
+      <c r="O262" t="n">
+        <v>0</v>
+      </c>
+      <c r="R262" t="n">
+        <v>0</v>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO262" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP262" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR262" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr"/>
+      <c r="AT262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU262" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV262" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW262" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX262" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY262" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA262" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB262" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC262" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -47693,7 +47838,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -47776,7 +47921,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10">
@@ -47786,7 +47931,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d045/2026-2029.xlsx
+++ b/diseases/d045/2026-2029.xlsx
@@ -47805,6 +47805,151 @@
         </is>
       </c>
     </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N263" t="n">
+        <v>1</v>
+      </c>
+      <c r="O263" t="n">
+        <v>1</v>
+      </c>
+      <c r="R263" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO263" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP263" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR263" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr"/>
+      <c r="AT263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU263" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV263" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW263" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX263" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY263" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA263" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB263" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC263" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -47838,7 +47983,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -47921,7 +48066,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10">
@@ -47931,7 +48076,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11">
@@ -47983,7 +48128,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5152</v>
+        <v>5153</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d045/2026-2029.xlsx
+++ b/diseases/d045/2026-2029.xlsx
@@ -39130,12 +39130,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -39244,7 +39244,7 @@
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
@@ -39281,12 +39281,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -39367,7 +39367,7 @@
       </c>
       <c r="AC214" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-FJ:national</t>
         </is>
       </c>
       <c r="AD214" t="inlineStr">
@@ -39478,7 +39478,7 @@
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
@@ -39515,12 +39515,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -39629,7 +39629,7 @@
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
@@ -39666,12 +39666,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -39752,7 +39752,7 @@
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD216" t="inlineStr">
@@ -39863,7 +39863,7 @@
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
@@ -39900,12 +39900,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -39939,10 +39939,10 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S217" t="inlineStr">
         <is>
@@ -40014,7 +40014,7 @@
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
@@ -40051,12 +40051,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -40090,10 +40090,10 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U218" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr">
@@ -40248,7 +40248,7 @@
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
@@ -40285,12 +40285,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -40399,7 +40399,7 @@
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
@@ -40436,12 +40436,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -40522,7 +40522,7 @@
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD220" t="inlineStr">
@@ -40633,7 +40633,7 @@
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
@@ -40670,12 +40670,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -40709,10 +40709,10 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>655</v>
+        <v>1</v>
       </c>
       <c r="O221" t="n">
-        <v>655</v>
+        <v>1</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
@@ -40784,7 +40784,7 @@
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
@@ -40821,12 +40821,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -40860,10 +40860,10 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>655</v>
+        <v>1</v>
       </c>
       <c r="O222" t="n">
-        <v>655</v>
+        <v>1</v>
       </c>
       <c r="U222" t="inlineStr">
         <is>
@@ -40907,7 +40907,7 @@
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD222" t="inlineStr">
@@ -41018,7 +41018,7 @@
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
@@ -41055,12 +41055,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -41094,10 +41094,10 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>1</v>
+        <v>655</v>
       </c>
       <c r="O223" t="n">
-        <v>1</v>
+        <v>655</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
@@ -41169,7 +41169,7 @@
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
@@ -41206,12 +41206,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -41245,10 +41245,10 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>1</v>
+        <v>655</v>
       </c>
       <c r="O224" t="n">
-        <v>1</v>
+        <v>655</v>
       </c>
       <c r="U224" t="inlineStr">
         <is>
@@ -41292,7 +41292,7 @@
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD224" t="inlineStr">
@@ -41403,7 +41403,7 @@
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
@@ -41440,12 +41440,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -41479,22 +41479,14 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O225" t="n">
-        <v>0</v>
-      </c>
-      <c r="R225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U225" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -41509,22 +41501,17 @@
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ225" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR225" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS225" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_230</t>
+          <t>SER_CN_PROV_DC_ECHINOCOCCOSIS; SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="AT225" t="n">
@@ -41532,47 +41519,47 @@
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -41604,12 +41591,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -41643,29 +41630,29 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_230</t>
+          <t>SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="V226" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_230</t>
+          <t>SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X226" t="inlineStr">
         <is>
-          <t>Echinococcus</t>
+          <t>包虫病</t>
         </is>
       </c>
       <c r="Y226" t="inlineStr">
@@ -41675,7 +41662,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -41690,7 +41677,7 @@
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN-SH:national</t>
         </is>
       </c>
       <c r="AD226" t="inlineStr">
@@ -41725,17 +41712,17 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN226" t="b">
@@ -41748,22 +41735,17 @@
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ226" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR226" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_230</t>
+          <t>SER_CN_PROV_DC_ECHINOCOCCOSIS; SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="AT226" t="n">
@@ -41771,47 +41753,47 @@
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -41843,12 +41825,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -41897,7 +41879,7 @@
       </c>
       <c r="U227" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -41917,7 +41899,7 @@
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
@@ -41927,7 +41909,7 @@
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT227" t="n">
@@ -41935,47 +41917,47 @@
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -42007,12 +41989,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -42053,22 +42035,22 @@
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="V228" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="W228" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X228" t="inlineStr">
         <is>
-          <t>Ekinokokkose</t>
+          <t>Echinococcus</t>
         </is>
       </c>
       <c r="Y228" t="inlineStr">
@@ -42093,7 +42075,7 @@
       </c>
       <c r="AC228" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD228" t="inlineStr">
@@ -42128,17 +42110,17 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
         </is>
       </c>
       <c r="AM228" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN228" t="b">
@@ -42156,7 +42138,7 @@
       </c>
       <c r="AQ228" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR228" t="inlineStr">
@@ -42166,7 +42148,7 @@
       </c>
       <c r="AS228" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT228" t="n">
@@ -42174,47 +42156,47 @@
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -42246,12 +42228,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -42285,13 +42267,13 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R229" t="n">
-        <v>0.009344880428283346</v>
+        <v>0</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
@@ -42300,7 +42282,7 @@
       </c>
       <c r="U229" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -42330,7 +42312,7 @@
       </c>
       <c r="AS229" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT229" t="n">
@@ -42343,42 +42325,42 @@
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -42410,12 +42392,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -42449,29 +42431,29 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="V230" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="W230" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X230" t="inlineStr">
         <is>
-          <t>Echinokockinfektion</t>
+          <t>Ekinokokkose</t>
         </is>
       </c>
       <c r="Y230" t="inlineStr">
@@ -42496,7 +42478,7 @@
       </c>
       <c r="AC230" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD230" t="inlineStr">
@@ -42531,17 +42513,17 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN230" t="b">
@@ -42569,7 +42551,7 @@
       </c>
       <c r="AS230" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT230" t="n">
@@ -42582,42 +42564,42 @@
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -42649,12 +42631,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -42679,7 +42661,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -42688,81 +42670,100 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R231" t="n">
-        <v>0</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ231" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR231" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS231" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
       <c r="AT231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -42789,17 +42790,17 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -42824,7 +42825,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -42833,81 +42834,175 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O232" t="n">
-        <v>0</v>
-      </c>
-      <c r="R232" t="n">
-        <v>0</v>
-      </c>
-      <c r="S232" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>Echinokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD232" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF232" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG232" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI232" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ232" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK232" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM232" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN232" t="b">
+        <v>1</v>
       </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ232" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR232" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS232" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
       <c r="AT232" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -42969,7 +43064,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -43114,7 +43209,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -43259,7 +43354,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -43268,13 +43363,13 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R235" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
@@ -43374,12 +43469,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -43404,12 +43499,12 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N236" t="n">
@@ -43452,42 +43547,42 @@
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43519,12 +43614,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -43549,23 +43644,26 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O237" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R237" t="n">
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO237" t="inlineStr">
@@ -43594,42 +43692,42 @@
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43661,12 +43759,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -43705,9 +43803,12 @@
       <c r="O238" t="n">
         <v>0</v>
       </c>
+      <c r="R238" t="n">
+        <v>0</v>
+      </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO238" t="inlineStr">
@@ -43741,12 +43842,12 @@
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
@@ -43761,12 +43862,12 @@
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
@@ -43803,12 +43904,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -43883,7 +43984,7 @@
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
@@ -43903,7 +44004,7 @@
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
@@ -43945,12 +44046,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -44025,7 +44126,7 @@
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
@@ -44045,7 +44146,7 @@
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
@@ -44087,12 +44188,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -44167,7 +44268,7 @@
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
@@ -44187,7 +44288,7 @@
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
@@ -44229,12 +44330,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -44309,7 +44410,7 @@
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
@@ -44329,7 +44430,7 @@
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
@@ -44371,12 +44472,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -44451,7 +44552,7 @@
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
@@ -44471,7 +44572,7 @@
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
@@ -44513,12 +44614,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -44593,7 +44694,7 @@
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
@@ -44613,7 +44714,7 @@
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
@@ -44655,12 +44756,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -44694,20 +44795,14 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>326</v>
+        <v>0</v>
       </c>
       <c r="O245" t="n">
-        <v>326</v>
-      </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
-      <c r="R245" t="n">
-        <v>0.02307288197162032</v>
+        <v>0</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO245" t="inlineStr">
@@ -44736,42 +44831,42 @@
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -44803,12 +44898,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -44842,100 +44937,78 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O246" t="n">
-        <v>1</v>
-      </c>
-      <c r="R246" t="n">
-        <v>0.01778809170864137</v>
+        <v>0</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U246" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="AA246" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO246" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ246" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR246" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS246" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr"/>
       <c r="AT246" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -44962,17 +45035,17 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -45006,175 +45079,84 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>1</v>
+        <v>326</v>
       </c>
       <c r="O247" t="n">
-        <v>1</v>
-      </c>
-      <c r="U247" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="V247" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="W247" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X247" t="inlineStr">
-        <is>
-          <t>Echinococcus</t>
-        </is>
-      </c>
-      <c r="Y247" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z247" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA247" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB247" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC247" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD247" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE247" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF247" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG247" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH247" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI247" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ247" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK247" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
-        </is>
-      </c>
-      <c r="AM247" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN247" t="b">
-        <v>1</v>
+        <v>326</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>0</v>
+      </c>
+      <c r="R247" t="n">
+        <v>0.02307288197162032</v>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ247" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR247" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS247" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr"/>
       <c r="AT247" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -45206,12 +45188,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -45245,22 +45227,14 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O248" t="n">
-        <v>2</v>
-      </c>
-      <c r="R248" t="n">
-        <v>0.03537951651591013</v>
+        <v>1</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U248" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -45275,7 +45249,7 @@
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ248" t="inlineStr">
@@ -45283,14 +45257,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR248" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS248" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_CN_PROV_DC_ECHINOCOCCOSIS; SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="AT248" t="n">
@@ -45298,47 +45267,47 @@
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -45370,12 +45339,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -45409,29 +45378,29 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="V249" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="W249" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X249" t="inlineStr">
         <is>
-          <t>Ekinokokkose</t>
+          <t>包虫病</t>
         </is>
       </c>
       <c r="Y249" t="inlineStr">
@@ -45441,7 +45410,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -45456,7 +45425,7 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CN-CQ:national</t>
         </is>
       </c>
       <c r="AD249" t="inlineStr">
@@ -45491,17 +45460,17 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -45514,7 +45483,7 @@
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ249" t="inlineStr">
@@ -45522,14 +45491,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR249" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS249" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_CN_PROV_DC_ECHINOCOCCOSIS; SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="AT249" t="n">
@@ -45537,47 +45501,47 @@
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -45609,12 +45573,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -45653,17 +45617,9 @@
       <c r="O250" t="n">
         <v>0</v>
       </c>
-      <c r="R250" t="n">
-        <v>0</v>
-      </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U250" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -45678,7 +45634,7 @@
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ250" t="inlineStr">
@@ -45686,14 +45642,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR250" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS250" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_CN_PROV_DC_ECHINOCOCCOSIS; SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="AT250" t="n">
@@ -45701,47 +45652,47 @@
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -45773,12 +45724,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -45819,22 +45770,22 @@
       </c>
       <c r="U251" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="V251" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="W251" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X251" t="inlineStr">
         <is>
-          <t>Echinokockinfektion</t>
+          <t>包虫病</t>
         </is>
       </c>
       <c r="Y251" t="inlineStr">
@@ -45844,7 +45795,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -45859,7 +45810,7 @@
       </c>
       <c r="AC251" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD251" t="inlineStr">
@@ -45894,17 +45845,17 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -45917,7 +45868,7 @@
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ251" t="inlineStr">
@@ -45925,14 +45876,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR251" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS251" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_CN_PROV_DC_ECHINOCOCCOSIS; SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="AT251" t="n">
@@ -45940,47 +45886,47 @@
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -46012,12 +45958,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -46042,7 +45988,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -46051,81 +45997,87 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O252" t="n">
-        <v>3</v>
-      </c>
-      <c r="R252" t="n">
-        <v>0.002450425222697299</v>
+        <v>0</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR252" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS252" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ252" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_ECHINOCOCCOSIS; SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
       <c r="AT252" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -46152,17 +46104,17 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -46187,7 +46139,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -46201,76 +46153,165 @@
       <c r="O253" t="n">
         <v>0</v>
       </c>
-      <c r="R253" t="n">
-        <v>0</v>
-      </c>
-      <c r="S253" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>country:CN-HN:national</t>
+        </is>
+      </c>
+      <c r="AD253" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF253" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG253" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH253" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI253" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ253" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK253" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM253" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN253" t="b">
+        <v>1</v>
       </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR253" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS253" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ253" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_ECHINOCOCCOSIS; SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
       <c r="AT253" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -46302,12 +46343,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -46332,7 +46373,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -46341,81 +46382,87 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O254" t="n">
-        <v>1</v>
-      </c>
-      <c r="R254" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR254" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS254" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ254" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_ECHINOCOCCOSIS; SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
       <c r="AT254" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -46442,17 +46489,17 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -46477,7 +46524,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -46491,76 +46538,165 @@
       <c r="O255" t="n">
         <v>0</v>
       </c>
-      <c r="R255" t="n">
-        <v>0</v>
-      </c>
-      <c r="S255" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD255" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF255" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG255" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH255" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ255" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK255" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM255" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN255" t="b">
+        <v>1</v>
       </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR255" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS255" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ255" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_ECHINOCOCCOSIS; SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
       <c r="AT255" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -46592,12 +46728,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -46622,7 +46758,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -46636,76 +46772,82 @@
       <c r="O256" t="n">
         <v>1</v>
       </c>
-      <c r="R256" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO256" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR256" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ256" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_ECHINOCOCCOSIS; SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
       <c r="AT256" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -46732,17 +46874,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -46767,90 +46909,179 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O257" t="n">
-        <v>0</v>
-      </c>
-      <c r="R257" t="n">
-        <v>0</v>
-      </c>
-      <c r="S257" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>country:CN-LN:national</t>
+        </is>
+      </c>
+      <c r="AD257" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE257" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF257" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG257" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH257" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI257" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ257" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM257" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN257" t="b">
+        <v>1</v>
       </c>
       <c r="AO257" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR257" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS257" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ257" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_ECHINOCOCCOSIS; SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
       <c r="AT257" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -46882,12 +47113,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -46912,31 +47143,23 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N258" t="n">
-        <v>0</v>
+        <v>4967</v>
       </c>
       <c r="O258" t="n">
-        <v>0</v>
-      </c>
-      <c r="R258" t="n">
-        <v>0</v>
+        <v>4967</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U258" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
@@ -46951,22 +47174,17 @@
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ258" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR258" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS258" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_230</t>
+          <t>SER_CN_PROV_DC_ECHINOCOCCOSIS; SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="AT258" t="n">
@@ -46974,47 +47192,47 @@
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -47046,12 +47264,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -47076,38 +47294,38 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N259" t="n">
-        <v>0</v>
+        <v>4967</v>
       </c>
       <c r="O259" t="n">
-        <v>0</v>
+        <v>4967</v>
       </c>
       <c r="U259" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_230</t>
+          <t>SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="V259" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_230</t>
+          <t>SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="W259" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X259" t="inlineStr">
         <is>
-          <t>Echinococcus</t>
+          <t>包虫病</t>
         </is>
       </c>
       <c r="Y259" t="inlineStr">
@@ -47117,7 +47335,7 @@
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
@@ -47132,7 +47350,7 @@
       </c>
       <c r="AC259" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD259" t="inlineStr">
@@ -47167,17 +47385,17 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN259" t="b">
@@ -47190,22 +47408,17 @@
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ259" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR259" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS259" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_230</t>
+          <t>SER_CN_PROV_DC_ECHINOCOCCOSIS; SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="AT259" t="n">
@@ -47213,47 +47426,47 @@
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -47285,12 +47498,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -47315,12 +47528,12 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N260" t="n">
@@ -47329,17 +47542,9 @@
       <c r="O260" t="n">
         <v>0</v>
       </c>
-      <c r="R260" t="n">
-        <v>0</v>
-      </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U260" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
@@ -47354,7 +47559,7 @@
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ260" t="inlineStr">
@@ -47362,14 +47567,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR260" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS260" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_CN_PROV_DC_ECHINOCOCCOSIS; SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="AT260" t="n">
@@ -47377,47 +47577,47 @@
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -47449,12 +47649,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -47479,12 +47679,12 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N261" t="n">
@@ -47495,22 +47695,22 @@
       </c>
       <c r="U261" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="V261" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="W261" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X261" t="inlineStr">
         <is>
-          <t>Ekinokokkose</t>
+          <t>包虫病</t>
         </is>
       </c>
       <c r="Y261" t="inlineStr">
@@ -47520,7 +47720,7 @@
       </c>
       <c r="Z261" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
@@ -47535,7 +47735,7 @@
       </c>
       <c r="AC261" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CN-SH:national</t>
         </is>
       </c>
       <c r="AD261" t="inlineStr">
@@ -47570,17 +47770,17 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -47593,7 +47793,7 @@
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ261" t="inlineStr">
@@ -47601,14 +47801,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR261" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS261" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_CN_PROV_DC_ECHINOCOCCOSIS; SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="AT261" t="n">
@@ -47616,47 +47811,47 @@
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -47688,12 +47883,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -47718,90 +47913,109 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R262" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S262" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ262" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR262" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS262" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
       <c r="AT262" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA262" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB262" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC262" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -47828,17 +48042,17 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -47863,12 +48077,12 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N263" t="n">
@@ -47877,74 +48091,2940 @@
       <c r="O263" t="n">
         <v>1</v>
       </c>
-      <c r="R263" t="n">
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>Echinococcus</t>
+        </is>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD263" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE263" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF263" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG263" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH263" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI263" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ263" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK263" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
+        </is>
+      </c>
+      <c r="AM263" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN263" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO263" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP263" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ263" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR263" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="AT263" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU263" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV263" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW263" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX263" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY263" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA263" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB263" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC263" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N264" t="n">
+        <v>2</v>
+      </c>
+      <c r="O264" t="n">
+        <v>2</v>
+      </c>
+      <c r="R264" t="n">
+        <v>0.03537951651591013</v>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO264" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP264" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ264" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR264" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT264" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU264" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV264" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW264" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX264" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY264" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA264" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB264" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC264" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N265" t="n">
+        <v>2</v>
+      </c>
+      <c r="O265" t="n">
+        <v>2</v>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>Ekinokokkose</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD265" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF265" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG265" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH265" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI265" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ265" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK265" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM265" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN265" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO265" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP265" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ265" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR265" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT265" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU265" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV265" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW265" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX265" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY265" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA265" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB265" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC265" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N266" t="n">
+        <v>0</v>
+      </c>
+      <c r="O266" t="n">
+        <v>0</v>
+      </c>
+      <c r="R266" t="n">
+        <v>0</v>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO266" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP266" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ266" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR266" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="AT266" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU266" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV266" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW266" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX266" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY266" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA266" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB266" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC266" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N267" t="n">
+        <v>0</v>
+      </c>
+      <c r="O267" t="n">
+        <v>0</v>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X267" t="inlineStr">
+        <is>
+          <t>Echinokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD267" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE267" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF267" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG267" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH267" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI267" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ267" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK267" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM267" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN267" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO267" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP267" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ267" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR267" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="AT267" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU267" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV267" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW267" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX267" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY267" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA267" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB267" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC267" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N268" t="n">
+        <v>3</v>
+      </c>
+      <c r="O268" t="n">
+        <v>3</v>
+      </c>
+      <c r="R268" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO268" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP268" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR268" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr"/>
+      <c r="AT268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU268" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV268" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW268" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX268" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY268" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA268" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB268" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC268" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N269" t="n">
+        <v>0</v>
+      </c>
+      <c r="O269" t="n">
+        <v>0</v>
+      </c>
+      <c r="R269" t="n">
+        <v>0</v>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO269" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP269" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR269" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr"/>
+      <c r="AT269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU269" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV269" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW269" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX269" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY269" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA269" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB269" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC269" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N270" t="n">
+        <v>1</v>
+      </c>
+      <c r="O270" t="n">
+        <v>1</v>
+      </c>
+      <c r="R270" t="n">
         <v>0.0008168084075657662</v>
       </c>
-      <c r="S263" t="inlineStr">
+      <c r="S270" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO263" t="inlineStr">
+      <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP263" t="inlineStr">
+      <c r="AP270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR263" t="inlineStr">
+      <c r="AR270" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS263" t="inlineStr"/>
-      <c r="AT263" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU263" t="inlineStr">
+      <c r="AS270" t="inlineStr"/>
+      <c r="AT270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU270" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV263" t="inlineStr">
+      <c r="AV270" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW263" t="inlineStr">
+      <c r="AW270" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX263" t="inlineStr">
+      <c r="AX270" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY263" t="inlineStr">
+      <c r="AY270" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ263" t="inlineStr">
+      <c r="AZ270" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA263" t="inlineStr">
+      <c r="BA270" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB263" t="inlineStr">
+      <c r="BB270" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC263" t="inlineStr">
+      <c r="BC270" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N271" t="n">
+        <v>0</v>
+      </c>
+      <c r="O271" t="n">
+        <v>0</v>
+      </c>
+      <c r="R271" t="n">
+        <v>0</v>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO271" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP271" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR271" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr"/>
+      <c r="AT271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU271" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV271" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW271" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX271" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY271" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA271" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB271" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC271" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N272" t="n">
+        <v>1</v>
+      </c>
+      <c r="O272" t="n">
+        <v>1</v>
+      </c>
+      <c r="R272" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO272" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP272" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR272" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr"/>
+      <c r="AT272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU272" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV272" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW272" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX272" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY272" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA272" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB272" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC272" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N273" t="n">
+        <v>0</v>
+      </c>
+      <c r="O273" t="n">
+        <v>0</v>
+      </c>
+      <c r="R273" t="n">
+        <v>0</v>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO273" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP273" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR273" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr"/>
+      <c r="AT273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU273" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV273" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW273" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX273" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY273" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA273" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB273" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC273" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N274" t="n">
+        <v>0</v>
+      </c>
+      <c r="O274" t="n">
+        <v>0</v>
+      </c>
+      <c r="R274" t="n">
+        <v>0</v>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO274" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP274" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ274" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR274" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="AT274" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU274" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV274" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW274" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX274" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY274" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA274" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB274" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC274" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N275" t="n">
+        <v>0</v>
+      </c>
+      <c r="O275" t="n">
+        <v>0</v>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>Echinococcus</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB275" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD275" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE275" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF275" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG275" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH275" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI275" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ275" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK275" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
+        </is>
+      </c>
+      <c r="AM275" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN275" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO275" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP275" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ275" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR275" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS275" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="AT275" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU275" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV275" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW275" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX275" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY275" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA275" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB275" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC275" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N276" t="n">
+        <v>0</v>
+      </c>
+      <c r="O276" t="n">
+        <v>0</v>
+      </c>
+      <c r="R276" t="n">
+        <v>0</v>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO276" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP276" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ276" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR276" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS276" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT276" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU276" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV276" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW276" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX276" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY276" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA276" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB276" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC276" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N277" t="n">
+        <v>0</v>
+      </c>
+      <c r="O277" t="n">
+        <v>0</v>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>Ekinokokkose</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD277" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE277" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF277" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG277" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH277" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI277" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ277" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK277" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM277" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN277" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO277" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP277" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ277" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR277" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT277" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU277" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV277" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW277" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX277" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY277" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA277" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB277" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC277" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N278" t="n">
+        <v>0</v>
+      </c>
+      <c r="O278" t="n">
+        <v>0</v>
+      </c>
+      <c r="R278" t="n">
+        <v>0</v>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO278" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP278" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR278" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr"/>
+      <c r="AT278" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU278" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV278" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW278" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX278" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY278" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA278" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB278" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC278" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N279" t="n">
+        <v>1</v>
+      </c>
+      <c r="O279" t="n">
+        <v>1</v>
+      </c>
+      <c r="R279" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO279" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP279" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR279" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS279" t="inlineStr"/>
+      <c r="AT279" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU279" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV279" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW279" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX279" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY279" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA279" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB279" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC279" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -48066,7 +51146,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10">
@@ -48076,7 +51156,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>262</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11">
@@ -48096,7 +51176,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -48128,7 +51208,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5153</v>
+        <v>10122</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d045/2026-2029.xlsx
+++ b/diseases/d045/2026-2029.xlsx
@@ -51030,6 +51030,554 @@
         </is>
       </c>
     </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N280" t="n">
+        <v>0</v>
+      </c>
+      <c r="O280" t="n">
+        <v>0</v>
+      </c>
+      <c r="R280" t="n">
+        <v>0</v>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO280" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP280" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR280" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr"/>
+      <c r="AT280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU280" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV280" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW280" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX280" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY280" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA280" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB280" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC280" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N281" t="n">
+        <v>0</v>
+      </c>
+      <c r="O281" t="n">
+        <v>0</v>
+      </c>
+      <c r="R281" t="n">
+        <v>0</v>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO281" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP281" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ281" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR281" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS281" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="AT281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU281" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV281" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW281" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX281" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY281" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA281" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB281" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC281" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N282" t="n">
+        <v>0</v>
+      </c>
+      <c r="O282" t="n">
+        <v>0</v>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X282" t="inlineStr">
+        <is>
+          <t>Echinococcus</t>
+        </is>
+      </c>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z282" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB282" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC282" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD282" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE282" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF282" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG282" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH282" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI282" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ282" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK282" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
+        </is>
+      </c>
+      <c r="AM282" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN282" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO282" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP282" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ282" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR282" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS282" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="AT282" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU282" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV282" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW282" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX282" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY282" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA282" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB282" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC282" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -51063,7 +51611,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -51146,7 +51694,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -51156,7 +51704,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11">
@@ -51176,7 +51724,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d045/2026-2029.xlsx
+++ b/diseases/d045/2026-2029.xlsx
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -22653,7 +22653,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -28602,7 +28602,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -35450,7 +35450,7 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN190" t="b">
@@ -42523,7 +42523,7 @@
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN230" t="b">
@@ -48581,7 +48581,7 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -50404,13 +50404,13 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O276" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R276" t="n">
-        <v>0</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
@@ -50568,10 +50568,10 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O277" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U277" t="inlineStr">
         <is>
@@ -50660,7 +50660,7 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN277" t="b">
@@ -51756,7 +51756,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10122</v>
+        <v>10124</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d045/2026-2029.xlsx
+++ b/diseases/d045/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1211,6 +1226,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1356,6 +1376,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1501,6 +1526,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1646,6 +1676,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1791,6 +1826,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1936,6 +1976,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2474,6 +2519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6730,7 +6780,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7888,6 +7938,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8033,6 +8088,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8178,6 +8238,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8323,6 +8388,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8468,6 +8538,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8613,6 +8688,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8758,6 +8838,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8903,6 +8988,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9048,6 +9138,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9586,6 +9681,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13842,7 +13942,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15000,6 +15100,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15145,6 +15250,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15290,6 +15400,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15435,6 +15550,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15580,6 +15700,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15725,6 +15850,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15870,6 +16000,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16015,6 +16150,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16160,6 +16300,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16698,6 +16843,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20569,7 +20719,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -21724,6 +21874,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21869,6 +22024,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22014,6 +22174,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22159,6 +22324,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22304,6 +22474,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22449,6 +22624,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22594,6 +22774,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22739,6 +22924,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22884,6 +23074,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23422,6 +23617,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27293,7 +27493,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -28448,6 +28648,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28593,6 +28798,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28738,6 +28948,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28883,6 +29098,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29028,6 +29248,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29173,6 +29398,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29318,6 +29548,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29463,6 +29698,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29608,6 +29848,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30146,6 +30391,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34402,7 +34652,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -35705,6 +35955,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35850,6 +36105,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35995,6 +36255,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36140,6 +36405,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36285,6 +36555,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36430,6 +36705,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36575,6 +36855,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36720,6 +37005,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36865,6 +37155,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37403,6 +37698,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41274,7 +41574,7 @@
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN230" t="b">
@@ -42417,6 +42717,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42562,6 +42867,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42707,6 +43017,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42852,6 +43167,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42997,6 +43317,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43142,6 +43467,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43287,6 +43617,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43432,6 +43767,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43577,6 +43917,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44115,6 +44460,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48371,7 +48721,7 @@
       </c>
       <c r="AM270" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN270" t="b">
@@ -49659,6 +50009,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49804,6 +50159,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO279" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49949,6 +50309,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO280" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50094,6 +50459,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50239,6 +50609,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50384,6 +50759,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO283" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50529,6 +50909,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO284" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50674,6 +51059,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50819,6 +51209,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO286" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50912,12 +51307,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -50951,84 +51346,92 @@
         </is>
       </c>
       <c r="N287" t="n">
-        <v>326</v>
+        <v>0</v>
       </c>
       <c r="O287" t="n">
-        <v>326</v>
-      </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
-      <c r="R287" t="n">
-        <v>0.02307288197162032</v>
+        <v>0</v>
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ECHINOCOCCUS_MULTILOCULARIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO287" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP287" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR287" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS287" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ287" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS287" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ECHINOCOCCUS_MULTILOCULARIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV287" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW287" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX287" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ287" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA287" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB287" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC287" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -51055,17 +51458,17 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -51099,87 +51502,170 @@
         </is>
       </c>
       <c r="N288" t="n">
+        <v>0</v>
+      </c>
+      <c r="O288" t="n">
+        <v>0</v>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ECHINOCOCCUS_MULTILOCULARIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ECHINOCOCCUS_MULTILOCULARIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X288" t="inlineStr">
+        <is>
+          <t>Echinococcus Multilocularis Infection</t>
+        </is>
+      </c>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC288" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD288" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE288" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF288" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG288" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH288" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI288" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ288" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK288" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary Echinococcus multilocularis infection notifications; confirmed cases only. This species-specific source category is narrower than the ontology's all-echinococcosis D045 concept.</t>
+        </is>
+      </c>
+      <c r="AM288" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN288" t="b">
         <v>1</v>
       </c>
-      <c r="O288" t="n">
+      <c r="AO288" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP288" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ288" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS288" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ECHINOCOCCUS_MULTILOCULARIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT288" t="n">
         <v>1</v>
       </c>
-      <c r="S288" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AA288" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO288" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP288" t="inlineStr">
-        <is>
-          <t>priority_overlay</t>
-        </is>
-      </c>
-      <c r="AQ288" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS288" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_ECHINOCOCCOSIS; SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
-        </is>
-      </c>
-      <c r="AT288" t="n">
-        <v>2</v>
-      </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV288" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW288" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ288" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA288" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB288" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC288" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -51206,17 +51692,17 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -51250,39 +51736,20 @@
         </is>
       </c>
       <c r="N289" t="n">
-        <v>1</v>
+        <v>326</v>
       </c>
       <c r="O289" t="n">
-        <v>1</v>
-      </c>
-      <c r="U289" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
-        </is>
-      </c>
-      <c r="V289" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
-        </is>
-      </c>
-      <c r="W289" t="inlineStr">
-        <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
-        </is>
-      </c>
-      <c r="X289" t="inlineStr">
-        <is>
-          <t>包虫病</t>
-        </is>
-      </c>
-      <c r="Y289" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z289" t="inlineStr">
-        <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        <v>326</v>
+      </c>
+      <c r="Q289" t="n">
+        <v>0</v>
+      </c>
+      <c r="R289" t="n">
+        <v>0.02307288197162032</v>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
@@ -51290,130 +51757,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB289" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC289" t="inlineStr">
-        <is>
-          <t>country:CN-CQ:national</t>
-        </is>
-      </c>
-      <c r="AD289" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE289" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF289" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG289" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH289" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI289" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ289" t="inlineStr">
-        <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
-        </is>
-      </c>
-      <c r="AK289" t="inlineStr">
-        <is>
-          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
-        </is>
-      </c>
-      <c r="AM289" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN289" t="b">
-        <v>1</v>
-      </c>
       <c r="AO289" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP289" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
-        </is>
-      </c>
-      <c r="AQ289" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS289" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_ECHINOCOCCOSIS; SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR289" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS289" t="inlineStr"/>
       <c r="AT289" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU289" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV289" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW289" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ289" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA289" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB289" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC289" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -51445,12 +51850,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -51484,10 +51889,10 @@
         </is>
       </c>
       <c r="N290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S290" t="inlineStr">
         <is>
@@ -51559,7 +51964,7 @@
       </c>
       <c r="BB290" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC290" t="inlineStr">
@@ -51596,12 +52001,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -51635,10 +52040,10 @@
         </is>
       </c>
       <c r="N291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U291" t="inlineStr">
         <is>
@@ -51682,7 +52087,7 @@
       </c>
       <c r="AC291" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-CQ:national</t>
         </is>
       </c>
       <c r="AD291" t="inlineStr">
@@ -51793,7 +52198,7 @@
       </c>
       <c r="BB291" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC291" t="inlineStr">
@@ -51830,12 +52235,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -51944,7 +52349,7 @@
       </c>
       <c r="BB292" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC292" t="inlineStr">
@@ -51981,12 +52386,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -52067,7 +52472,7 @@
       </c>
       <c r="AC293" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD293" t="inlineStr">
@@ -52178,7 +52583,7 @@
       </c>
       <c r="BB293" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC293" t="inlineStr">
@@ -52215,12 +52620,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -52329,7 +52734,7 @@
       </c>
       <c r="BB294" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC294" t="inlineStr">
@@ -52366,12 +52771,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -52452,7 +52857,7 @@
       </c>
       <c r="AC295" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD295" t="inlineStr">
@@ -52563,7 +52968,7 @@
       </c>
       <c r="BB295" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC295" t="inlineStr">
@@ -52600,12 +53005,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -52639,10 +53044,10 @@
         </is>
       </c>
       <c r="N296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S296" t="inlineStr">
         <is>
@@ -52714,7 +53119,7 @@
       </c>
       <c r="BB296" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC296" t="inlineStr">
@@ -52751,12 +53156,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -52790,10 +53195,10 @@
         </is>
       </c>
       <c r="N297" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O297" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U297" t="inlineStr">
         <is>
@@ -52837,7 +53242,7 @@
       </c>
       <c r="AC297" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD297" t="inlineStr">
@@ -52948,7 +53353,7 @@
       </c>
       <c r="BB297" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC297" t="inlineStr">
@@ -52985,12 +53390,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -53024,10 +53429,10 @@
         </is>
       </c>
       <c r="N298" t="n">
-        <v>4967</v>
+        <v>1</v>
       </c>
       <c r="O298" t="n">
-        <v>4967</v>
+        <v>1</v>
       </c>
       <c r="S298" t="inlineStr">
         <is>
@@ -53099,7 +53504,7 @@
       </c>
       <c r="BB298" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC298" t="inlineStr">
@@ -53136,12 +53541,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -53175,10 +53580,10 @@
         </is>
       </c>
       <c r="N299" t="n">
-        <v>4967</v>
+        <v>1</v>
       </c>
       <c r="O299" t="n">
-        <v>4967</v>
+        <v>1</v>
       </c>
       <c r="U299" t="inlineStr">
         <is>
@@ -53222,7 +53627,7 @@
       </c>
       <c r="AC299" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD299" t="inlineStr">
@@ -53333,7 +53738,7 @@
       </c>
       <c r="BB299" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC299" t="inlineStr">
@@ -53370,12 +53775,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -53409,10 +53814,10 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>0</v>
+        <v>4967</v>
       </c>
       <c r="O300" t="n">
-        <v>0</v>
+        <v>4967</v>
       </c>
       <c r="S300" t="inlineStr">
         <is>
@@ -53484,7 +53889,7 @@
       </c>
       <c r="BB300" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC300" t="inlineStr">
@@ -53521,12 +53926,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -53560,10 +53965,10 @@
         </is>
       </c>
       <c r="N301" t="n">
-        <v>0</v>
+        <v>4967</v>
       </c>
       <c r="O301" t="n">
-        <v>0</v>
+        <v>4967</v>
       </c>
       <c r="U301" t="inlineStr">
         <is>
@@ -53607,7 +54012,7 @@
       </c>
       <c r="AC301" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD301" t="inlineStr">
@@ -53718,7 +54123,7 @@
       </c>
       <c r="BB301" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC301" t="inlineStr">
@@ -53755,12 +54160,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -53794,22 +54199,14 @@
         </is>
       </c>
       <c r="N302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O302" t="n">
-        <v>1</v>
-      </c>
-      <c r="R302" t="n">
-        <v>0.01778809170864137</v>
+        <v>0</v>
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U302" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
@@ -53824,22 +54221,17 @@
       </c>
       <c r="AP302" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ302" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR302" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS302" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_230</t>
+          <t>SER_CN_PROV_DC_ECHINOCOCCOSIS; SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="AT302" t="n">
@@ -53847,47 +54239,47 @@
       </c>
       <c r="AU302" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV302" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW302" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX302" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY302" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ302" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA302" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB302" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC302" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -53919,12 +54311,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -53958,29 +54350,29 @@
         </is>
       </c>
       <c r="N303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U303" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_230</t>
+          <t>SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="V303" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_230</t>
+          <t>SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="W303" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X303" t="inlineStr">
         <is>
-          <t>Echinococcus</t>
+          <t>包虫病</t>
         </is>
       </c>
       <c r="Y303" t="inlineStr">
@@ -53990,7 +54382,7 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
@@ -54005,7 +54397,7 @@
       </c>
       <c r="AC303" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN-SH:national</t>
         </is>
       </c>
       <c r="AD303" t="inlineStr">
@@ -54040,17 +54432,17 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM303" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN303" t="b">
@@ -54063,22 +54455,17 @@
       </c>
       <c r="AP303" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ303" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR303" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS303" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_230</t>
+          <t>SER_CN_PROV_DC_ECHINOCOCCOSIS; SER_CN_PROV_REPORT_ECHINOCOCCOSIS</t>
         </is>
       </c>
       <c r="AT303" t="n">
@@ -54086,47 +54473,47 @@
       </c>
       <c r="AU303" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV303" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW303" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ303" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA303" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB303" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC303" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -54158,12 +54545,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -54197,13 +54584,13 @@
         </is>
       </c>
       <c r="N304" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O304" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R304" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S304" t="inlineStr">
         <is>
@@ -54212,7 +54599,7 @@
       </c>
       <c r="U304" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
@@ -54232,7 +54619,7 @@
       </c>
       <c r="AQ304" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR304" t="inlineStr">
@@ -54242,7 +54629,7 @@
       </c>
       <c r="AS304" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT304" t="n">
@@ -54250,47 +54637,47 @@
       </c>
       <c r="AU304" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV304" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW304" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ304" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA304" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB304" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC304" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -54322,12 +54709,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -54361,29 +54748,29 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O305" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U305" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="V305" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="W305" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X305" t="inlineStr">
         <is>
-          <t>Ekinokokkose</t>
+          <t>Echinococcus</t>
         </is>
       </c>
       <c r="Y305" t="inlineStr">
@@ -54408,7 +54795,7 @@
       </c>
       <c r="AC305" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD305" t="inlineStr">
@@ -54443,17 +54830,17 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
         </is>
       </c>
       <c r="AM305" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN305" t="b">
@@ -54471,7 +54858,7 @@
       </c>
       <c r="AQ305" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR305" t="inlineStr">
@@ -54481,7 +54868,7 @@
       </c>
       <c r="AS305" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT305" t="n">
@@ -54489,47 +54876,47 @@
       </c>
       <c r="AU305" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV305" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW305" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ305" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA305" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB305" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC305" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -54561,12 +54948,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -54600,13 +54987,13 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O306" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R306" t="n">
-        <v>0</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S306" t="inlineStr">
         <is>
@@ -54615,7 +55002,7 @@
       </c>
       <c r="U306" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
@@ -54645,7 +55032,7 @@
       </c>
       <c r="AS306" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT306" t="n">
@@ -54658,42 +55045,42 @@
       </c>
       <c r="AV306" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW306" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY306" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ306" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA306" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB306" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC306" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -54725,12 +55112,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -54764,29 +55151,29 @@
         </is>
       </c>
       <c r="N307" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O307" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U307" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="V307" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="W307" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X307" t="inlineStr">
         <is>
-          <t>Echinokockinfektion</t>
+          <t>Ekinokokkose</t>
         </is>
       </c>
       <c r="Y307" t="inlineStr">
@@ -54811,7 +55198,7 @@
       </c>
       <c r="AC307" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD307" t="inlineStr">
@@ -54846,17 +55233,17 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM307" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN307" t="b">
@@ -54884,7 +55271,7 @@
       </c>
       <c r="AS307" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT307" t="n">
@@ -54897,42 +55284,42 @@
       </c>
       <c r="AV307" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW307" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX307" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY307" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ307" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA307" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB307" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC307" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -54964,12 +55351,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -54994,7 +55381,7 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -55003,81 +55390,100 @@
         </is>
       </c>
       <c r="N308" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O308" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R308" t="n">
-        <v>0.002450425222697299</v>
+        <v>0</v>
       </c>
       <c r="S308" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO308" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP308" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ308" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR308" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS308" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS308" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
       <c r="AT308" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU308" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV308" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW308" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ308" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA308" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB308" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC308" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -55104,17 +55510,17 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -55139,7 +55545,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -55153,76 +55559,170 @@
       <c r="O309" t="n">
         <v>0</v>
       </c>
-      <c r="R309" t="n">
-        <v>0</v>
-      </c>
-      <c r="S309" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="V309" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="W309" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X309" t="inlineStr">
+        <is>
+          <t>Echinokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y309" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z309" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB309" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC309" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD309" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE309" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF309" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG309" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH309" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI309" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ309" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK309" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM309" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN309" t="b">
+        <v>1</v>
       </c>
       <c r="AO309" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP309" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ309" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR309" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS309" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS309" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
       <c r="AT309" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU309" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV309" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ309" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA309" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB309" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC309" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -55284,7 +55784,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -55293,13 +55793,13 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O310" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R310" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S310" t="inlineStr">
         <is>
@@ -55429,7 +55929,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -55574,7 +56074,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -55689,12 +56189,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -55719,12 +56219,12 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N313" t="n">
@@ -55767,42 +56267,42 @@
       </c>
       <c r="AV313" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW313" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX313" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY313" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ313" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA313" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB313" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC313" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -55834,12 +56334,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -55864,26 +56364,26 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R314" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO314" t="inlineStr">
@@ -55912,42 +56412,42 @@
       </c>
       <c r="AV314" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW314" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX314" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY314" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ314" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA314" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB314" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC314" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -55979,12 +56479,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -56028,7 +56528,12 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO315" t="inlineStr">
@@ -56062,12 +56567,12 @@
       </c>
       <c r="AW315" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr">
@@ -56082,12 +56587,12 @@
       </c>
       <c r="BA315" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB315" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC315" t="inlineStr">
@@ -56124,12 +56629,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -56174,6 +56679,11 @@
       <c r="S316" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO316" t="inlineStr">
@@ -56207,7 +56717,7 @@
       </c>
       <c r="AW316" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX316" t="inlineStr">
@@ -56227,7 +56737,7 @@
       </c>
       <c r="BA316" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB316" t="inlineStr">
@@ -56269,12 +56779,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -56319,6 +56829,11 @@
       <c r="S317" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO317" t="inlineStr">
@@ -56352,7 +56867,7 @@
       </c>
       <c r="AW317" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX317" t="inlineStr">
@@ -56372,7 +56887,7 @@
       </c>
       <c r="BA317" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB317" t="inlineStr">
@@ -56414,12 +56929,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -56464,6 +56979,11 @@
       <c r="S318" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO318" t="inlineStr">
@@ -56497,7 +57017,7 @@
       </c>
       <c r="AW318" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX318" t="inlineStr">
@@ -56517,7 +57037,7 @@
       </c>
       <c r="BA318" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB318" t="inlineStr">
@@ -56559,12 +57079,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -56609,6 +57129,11 @@
       <c r="S319" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO319" t="inlineStr">
@@ -56642,7 +57167,7 @@
       </c>
       <c r="AW319" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX319" t="inlineStr">
@@ -56662,7 +57187,7 @@
       </c>
       <c r="BA319" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB319" t="inlineStr">
@@ -56704,12 +57229,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -56754,6 +57279,11 @@
       <c r="S320" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO320" t="inlineStr">
@@ -56787,7 +57317,7 @@
       </c>
       <c r="AW320" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX320" t="inlineStr">
@@ -56807,7 +57337,7 @@
       </c>
       <c r="BA320" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB320" t="inlineStr">
@@ -56849,12 +57379,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -56899,6 +57429,11 @@
       <c r="S321" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO321" t="inlineStr">
@@ -56932,7 +57467,7 @@
       </c>
       <c r="AW321" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX321" t="inlineStr">
@@ -56952,7 +57487,7 @@
       </c>
       <c r="BA321" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB321" t="inlineStr">
@@ -56994,12 +57529,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -57043,12 +57578,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U322" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -57058,75 +57588,66 @@
       </c>
       <c r="AO322" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP322" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ322" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR322" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS322" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS322" t="inlineStr"/>
       <c r="AT322" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU322" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV322" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW322" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX322" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY322" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ322" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA322" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB322" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC322" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -57153,17 +57674,17 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -57202,34 +57723,12 @@
       <c r="O323" t="n">
         <v>0</v>
       </c>
-      <c r="U323" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="V323" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="W323" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X323" t="inlineStr">
-        <is>
-          <t>Echinococcus</t>
-        </is>
-      </c>
-      <c r="Y323" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z323" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="R323" t="n">
+        <v>0</v>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
@@ -57237,135 +57736,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB323" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC323" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD323" t="inlineStr">
+      <c r="AO323" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP323" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR323" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS323" t="inlineStr"/>
+      <c r="AT323" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU323" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV323" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE323" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF323" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG323" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH323" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI323" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ323" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK323" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
-        </is>
-      </c>
-      <c r="AM323" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN323" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO323" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP323" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ323" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR323" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS323" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="AT323" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU323" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV323" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW323" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX323" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY323" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ323" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA323" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB323" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC323" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -57397,12 +57829,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -57436,13 +57868,13 @@
         </is>
       </c>
       <c r="N324" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O324" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R324" t="n">
-        <v>0.03537951651591013</v>
+        <v>0</v>
       </c>
       <c r="S324" t="inlineStr">
         <is>
@@ -57451,7 +57883,7 @@
       </c>
       <c r="U324" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -57471,7 +57903,7 @@
       </c>
       <c r="AQ324" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR324" t="inlineStr">
@@ -57481,7 +57913,7 @@
       </c>
       <c r="AS324" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT324" t="n">
@@ -57489,47 +57921,47 @@
       </c>
       <c r="AU324" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV324" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW324" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX324" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY324" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ324" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA324" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB324" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC324" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -57561,12 +57993,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -57600,29 +58032,29 @@
         </is>
       </c>
       <c r="N325" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O325" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U325" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="V325" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="W325" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X325" t="inlineStr">
         <is>
-          <t>Ekinokokkose</t>
+          <t>Echinococcus</t>
         </is>
       </c>
       <c r="Y325" t="inlineStr">
@@ -57647,7 +58079,7 @@
       </c>
       <c r="AC325" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD325" t="inlineStr">
@@ -57682,17 +58114,17 @@
       </c>
       <c r="AJ325" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK325" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
         </is>
       </c>
       <c r="AM325" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN325" t="b">
@@ -57710,7 +58142,7 @@
       </c>
       <c r="AQ325" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR325" t="inlineStr">
@@ -57720,7 +58152,7 @@
       </c>
       <c r="AS325" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT325" t="n">
@@ -57728,47 +58160,47 @@
       </c>
       <c r="AU325" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV325" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW325" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX325" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY325" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ325" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA325" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB325" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC325" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -57800,12 +58232,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -57830,7 +58262,7 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -57839,81 +58271,100 @@
         </is>
       </c>
       <c r="N326" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O326" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R326" t="n">
-        <v>0</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S326" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO326" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP326" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ326" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR326" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS326" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS326" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT326" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU326" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV326" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW326" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX326" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY326" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ326" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA326" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB326" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC326" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -57940,17 +58391,17 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -57975,7 +58426,7 @@
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
@@ -57984,81 +58435,175 @@
         </is>
       </c>
       <c r="N327" t="n">
+        <v>2</v>
+      </c>
+      <c r="O327" t="n">
+        <v>2</v>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W327" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X327" t="inlineStr">
+        <is>
+          <t>Ekinokokkose</t>
+        </is>
+      </c>
+      <c r="Y327" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z327" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB327" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC327" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD327" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE327" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF327" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG327" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH327" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI327" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ327" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK327" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM327" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN327" t="b">
         <v>1</v>
       </c>
-      <c r="O327" t="n">
-        <v>1</v>
-      </c>
-      <c r="R327" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S327" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO327" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP327" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ327" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR327" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS327" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS327" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT327" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU327" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV327" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW327" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX327" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY327" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ327" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA327" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB327" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC327" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -58090,12 +58635,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -58120,7 +58665,7 @@
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
@@ -58129,81 +58674,100 @@
         </is>
       </c>
       <c r="N328" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O328" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R328" t="n">
-        <v>0</v>
+        <v>0.02803464128485004</v>
       </c>
       <c r="S328" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO328" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP328" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ328" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR328" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS328" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS328" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
       <c r="AT328" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU328" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV328" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW328" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX328" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY328" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ328" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA328" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB328" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC328" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -58230,17 +58794,17 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -58265,7 +58829,7 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -58274,81 +58838,175 @@
         </is>
       </c>
       <c r="N329" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O329" t="n">
-        <v>0</v>
-      </c>
-      <c r="R329" t="n">
-        <v>0</v>
-      </c>
-      <c r="S329" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="W329" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X329" t="inlineStr">
+        <is>
+          <t>Echinokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y329" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z329" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB329" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC329" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD329" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE329" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF329" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG329" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH329" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI329" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ329" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK329" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM329" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN329" t="b">
+        <v>1</v>
       </c>
       <c r="AO329" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP329" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ329" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR329" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS329" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS329" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
       <c r="AT329" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU329" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV329" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW329" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX329" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY329" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ329" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA329" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB329" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC329" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -58380,12 +59038,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -58410,12 +59068,12 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N330" t="n">
@@ -58432,87 +59090,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U330" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="AA330" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO330" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP330" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ330" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR330" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS330" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS330" t="inlineStr"/>
       <c r="AT330" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU330" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV330" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW330" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX330" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY330" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ330" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA330" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB330" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC330" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -58539,219 +59178,1221 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N331" t="n">
+        <v>1</v>
+      </c>
+      <c r="O331" t="n">
+        <v>1</v>
+      </c>
+      <c r="R331" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO331" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP331" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR331" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS331" t="inlineStr"/>
+      <c r="AT331" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU331" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV331" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW331" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX331" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY331" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA331" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB331" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC331" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N332" t="n">
+        <v>0</v>
+      </c>
+      <c r="O332" t="n">
+        <v>0</v>
+      </c>
+      <c r="R332" t="n">
+        <v>0</v>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO332" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP332" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR332" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS332" t="inlineStr"/>
+      <c r="AT332" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU332" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV332" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW332" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX332" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY332" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA332" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB332" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC332" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N333" t="n">
+        <v>0</v>
+      </c>
+      <c r="O333" t="n">
+        <v>0</v>
+      </c>
+      <c r="R333" t="n">
+        <v>0</v>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO333" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP333" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR333" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS333" t="inlineStr"/>
+      <c r="AT333" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU333" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV333" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW333" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX333" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY333" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA333" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB333" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC333" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N334" t="n">
+        <v>0</v>
+      </c>
+      <c r="O334" t="n">
+        <v>0</v>
+      </c>
+      <c r="R334" t="n">
+        <v>0</v>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO334" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP334" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ334" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR334" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS334" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="AT334" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU334" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV334" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW334" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX334" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY334" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA334" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB334" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC334" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F331" t="inlineStr">
+      <c r="F335" t="inlineStr">
         <is>
           <t>FI</t>
         </is>
       </c>
-      <c r="G331" t="inlineStr">
+      <c r="G335" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
-      <c r="H331" t="inlineStr">
-        <is>
-          <t>D045</t>
-        </is>
-      </c>
-      <c r="I331" t="inlineStr">
-        <is>
-          <t>Echinococcosis</t>
-        </is>
-      </c>
-      <c r="J331" t="inlineStr">
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
         <is>
           <t>包虫病</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr">
+      <c r="K335" t="inlineStr">
         <is>
           <t>Parasitic</t>
         </is>
       </c>
-      <c r="L331" t="inlineStr">
+      <c r="L335" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M331" t="inlineStr">
+      <c r="M335" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N331" t="n">
-        <v>0</v>
-      </c>
-      <c r="O331" t="n">
-        <v>0</v>
-      </c>
-      <c r="U331" t="inlineStr">
+      <c r="N335" t="n">
+        <v>0</v>
+      </c>
+      <c r="O335" t="n">
+        <v>0</v>
+      </c>
+      <c r="U335" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
-      <c r="V331" t="inlineStr">
+      <c r="V335" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
-      <c r="W331" t="inlineStr">
+      <c r="W335" t="inlineStr">
         <is>
           <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
-      <c r="X331" t="inlineStr">
+      <c r="X335" t="inlineStr">
         <is>
           <t>Echinococcus</t>
         </is>
       </c>
-      <c r="Y331" t="inlineStr">
+      <c r="Y335" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z331" t="inlineStr">
+      <c r="Z335" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA331" t="inlineStr">
+      <c r="AA335" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB331" t="inlineStr">
+      <c r="AB335" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC331" t="inlineStr">
+      <c r="AC335" t="inlineStr">
         <is>
           <t>country:FI:national</t>
         </is>
       </c>
-      <c r="AD331" t="inlineStr">
+      <c r="AD335" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE331" t="inlineStr">
+      <c r="AE335" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF331" t="inlineStr">
+      <c r="AF335" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG331" t="inlineStr">
+      <c r="AG335" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH331" t="inlineStr">
+      <c r="AH335" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI331" t="inlineStr">
+      <c r="AI335" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ331" t="inlineStr">
+      <c r="AJ335" t="inlineStr">
         <is>
           <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
-      <c r="AK331" t="inlineStr">
+      <c r="AK335" t="inlineStr">
         <is>
           <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
         </is>
       </c>
-      <c r="AM331" t="inlineStr">
+      <c r="AM335" t="inlineStr">
         <is>
           <t>provisional; raw</t>
         </is>
       </c>
-      <c r="AN331" t="b">
+      <c r="AN335" t="b">
         <v>1</v>
       </c>
-      <c r="AO331" t="inlineStr">
+      <c r="AO335" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP331" t="inlineStr">
+      <c r="AP335" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ331" t="inlineStr">
+      <c r="AQ335" t="inlineStr">
         <is>
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
-      <c r="AR331" t="inlineStr">
+      <c r="AR335" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS331" t="inlineStr">
+      <c r="AS335" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
-      <c r="AT331" t="n">
+      <c r="AT335" t="n">
         <v>2</v>
       </c>
-      <c r="AU331" t="inlineStr">
+      <c r="AU335" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
-      <c r="AV331" t="inlineStr">
+      <c r="AV335" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="AW331" t="inlineStr">
+      <c r="AW335" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="AX331" t="inlineStr">
+      <c r="AX335" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="AY331" t="inlineStr">
+      <c r="AY335" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
       </c>
-      <c r="AZ331" t="inlineStr">
+      <c r="AZ335" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="BA331" t="inlineStr">
+      <c r="BA335" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="BB331" t="inlineStr">
+      <c r="BB335" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="BC331" t="inlineStr">
+      <c r="BC335" t="inlineStr">
         <is>
           <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N336" t="n">
+        <v>0</v>
+      </c>
+      <c r="O336" t="n">
+        <v>0</v>
+      </c>
+      <c r="R336" t="n">
+        <v>0</v>
+      </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA336" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO336" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP336" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ336" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR336" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS336" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT336" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU336" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV336" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW336" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX336" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY336" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA336" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB336" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC336" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N337" t="n">
+        <v>0</v>
+      </c>
+      <c r="O337" t="n">
+        <v>0</v>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V337" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W337" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X337" t="inlineStr">
+        <is>
+          <t>Ekinokokkose</t>
+        </is>
+      </c>
+      <c r="Y337" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z337" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA337" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB337" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC337" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD337" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE337" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF337" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG337" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH337" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI337" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ337" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK337" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM337" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN337" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO337" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP337" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ337" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR337" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS337" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT337" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU337" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV337" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW337" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX337" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY337" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA337" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB337" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC337" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -58871,7 +60512,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10">
@@ -58881,7 +60522,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>330</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11">
@@ -58901,7 +60542,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -58933,7 +60574,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10124</v>
+        <v>10127</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d045/2026-2029.xlsx
+++ b/diseases/d045/2026-2029.xlsx
@@ -60396,6 +60396,151 @@
         </is>
       </c>
     </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N338" t="n">
+        <v>0</v>
+      </c>
+      <c r="O338" t="n">
+        <v>0</v>
+      </c>
+      <c r="R338" t="n">
+        <v>0</v>
+      </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO338" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP338" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR338" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS338" t="inlineStr"/>
+      <c r="AT338" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU338" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV338" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW338" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX338" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY338" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA338" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB338" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC338" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -60429,7 +60574,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -60512,7 +60657,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10">
@@ -60522,7 +60667,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="11">
